--- a/ibbotson.xlsx
+++ b/ibbotson.xlsx
@@ -8,14 +8,27 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ansa1\OneDrive\Desktop\corporate-bonds\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF22A101-EC22-45B0-A387-80CC638C235C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42C02FA9-93CE-49FF-8B1A-13587EA1D616}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="2" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -35,6 +48,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="165" formatCode="0.0000"/>
+  </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -105,7 +121,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -124,6 +140,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1454,8 +1473,8 @@
       <c r="B93" s="2">
         <v>2.4900000000000002</v>
       </c>
-      <c r="C93" s="3">
-        <v>2.6499999999999999E-2</v>
+      <c r="C93" s="8">
+        <v>1.8326597016962376E-2</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.3">
@@ -1465,8 +1484,8 @@
       <c r="B94" s="2">
         <v>2.4</v>
       </c>
-      <c r="C94" s="3">
-        <v>3.5400000000000001E-2</v>
+      <c r="C94" s="8">
+        <v>3.1282123925046035E-2</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.3">
@@ -1476,8 +1495,8 @@
       <c r="B95" s="2">
         <v>2.83</v>
       </c>
-      <c r="C95" s="3">
-        <v>1E-4</v>
+      <c r="C95" s="8">
+        <v>8.4038021812349317E-3</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.3">
@@ -1487,8 +1506,8 @@
       <c r="B96" s="2">
         <v>1.86</v>
       </c>
-      <c r="C96" s="3">
-        <v>8.72E-2</v>
+      <c r="C96" s="8">
+        <v>8.708692144400354E-2</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.3">
@@ -1498,8 +1517,8 @@
       <c r="B97" s="2">
         <v>0.93</v>
       </c>
-      <c r="C97" s="3">
-        <v>6.0999999999999999E-2</v>
+      <c r="C97" s="8">
+        <v>0.10811901242710809</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.3">
@@ -1509,8 +1528,8 @@
       <c r="B98" s="2">
         <v>1.47</v>
       </c>
-      <c r="C98" s="3">
-        <v>-1.54E-2</v>
+      <c r="C98" s="8">
+        <v>-3.7261235372969881E-2</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.3">
@@ -1520,8 +1539,8 @@
       <c r="B99" s="2">
         <v>3.62</v>
       </c>
-      <c r="C99" s="3">
-        <v>-0.13009999999999999</v>
+      <c r="C99" s="8">
+        <v>-0.13769242682515725</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.3">
@@ -1531,8 +1550,8 @@
       <c r="B100" s="2">
         <v>4.0199999999999996</v>
       </c>
-      <c r="C100" s="3">
-        <v>5.5300000000000002E-2</v>
+      <c r="C100" s="8">
+        <v>4.2422339622889993E-2</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.3">
@@ -1542,8 +1561,8 @@
       <c r="B101" s="2">
         <v>4.3899999999999997</v>
       </c>
-      <c r="C101" s="3">
-        <v>1.2500000000000001E-2</v>
+      <c r="C101" s="8">
+        <v>-2.924774839147104E-3</v>
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.3">
@@ -1553,8 +1572,8 @@
       <c r="B102" s="2">
         <v>4.1399999999999997</v>
       </c>
-      <c r="C102" s="3">
-        <v>7.2999999999999995E-2</v>
+      <c r="C102" s="8">
+        <v>8.4903480921744379E-2</v>
       </c>
     </row>
   </sheetData>

--- a/ibbotson.xlsx
+++ b/ibbotson.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ansa1\OneDrive\Desktop\corporate-bonds\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ansa1\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42C02FA9-93CE-49FF-8B1A-13587EA1D616}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25A46C0B-5877-43A3-80B6-013808E59D55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -49,7 +49,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="0.0000"/>
+    <numFmt numFmtId="164" formatCode="0.0000"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -142,7 +142,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -484,7 +484,7 @@
         <v>3.56</v>
       </c>
       <c r="C3" s="3">
-        <v>7.3700000000000002E-2</v>
+        <v>7.7700000000000005E-2</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
@@ -495,7 +495,7 @@
         <v>3.17</v>
       </c>
       <c r="C4" s="3">
-        <v>7.4399999999999994E-2</v>
+        <v>8.9300000000000004E-2</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
@@ -506,7 +506,7 @@
         <v>3.45</v>
       </c>
       <c r="C5" s="3">
-        <v>2.8400000000000002E-2</v>
+        <v>1E-3</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
@@ -517,7 +517,7 @@
         <v>3.36</v>
       </c>
       <c r="C6" s="3">
-        <v>3.27E-2</v>
+        <v>3.4200000000000001E-2</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
@@ -528,7 +528,7 @@
         <v>3.22</v>
       </c>
       <c r="C7" s="3">
-        <v>7.9799999999999996E-2</v>
+        <v>4.6600000000000003E-2</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
@@ -539,7 +539,7 @@
         <v>3.93</v>
       </c>
       <c r="C8" s="3">
-        <v>-1.8499999999999999E-2</v>
+        <v>-5.3100000000000001E-2</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
@@ -550,7 +550,7 @@
         <v>3.35</v>
       </c>
       <c r="C9" s="3">
-        <v>0.1082</v>
+        <v>0.16839999999999999</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
@@ -561,7 +561,7 @@
         <v>3.53</v>
       </c>
       <c r="C10" s="3">
-        <v>0.1038</v>
+        <v>-6.9999999999999999E-4</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
@@ -572,7 +572,7 @@
         <v>3.01</v>
       </c>
       <c r="C11" s="3">
-        <v>0.1384</v>
+        <v>0.1003</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
@@ -583,7 +583,7 @@
         <v>2.84</v>
       </c>
       <c r="C12" s="3">
-        <v>9.6100000000000005E-2</v>
+        <v>4.9799999999999997E-2</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
@@ -594,7 +594,7 @@
         <v>2.59</v>
       </c>
       <c r="C13" s="3">
-        <v>6.7400000000000002E-2</v>
+        <v>7.5200000000000003E-2</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
@@ -605,7 +605,7 @@
         <v>2.73</v>
       </c>
       <c r="C14" s="3">
-        <v>2.75E-2</v>
+        <v>2.3E-3</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
@@ -616,7 +616,7 @@
         <v>2.56</v>
       </c>
       <c r="C15" s="3">
-        <v>6.13E-2</v>
+        <v>5.5300000000000002E-2</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
@@ -627,7 +627,7 @@
         <v>2.35</v>
       </c>
       <c r="C16" s="3">
-        <v>3.9699999999999999E-2</v>
+        <v>5.9400000000000001E-2</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
@@ -638,7 +638,7 @@
         <v>2.0099999999999998</v>
       </c>
       <c r="C17" s="3">
-        <v>3.39E-2</v>
+        <v>6.0900000000000003E-2</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
@@ -649,7 +649,7 @@
         <v>2.4700000000000002</v>
       </c>
       <c r="C18" s="3">
-        <v>2.7300000000000001E-2</v>
+        <v>9.2999999999999992E-3</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
@@ -660,7 +660,7 @@
         <v>2.4900000000000002</v>
       </c>
       <c r="C19" s="3">
-        <v>2.5999999999999999E-2</v>
+        <v>3.2199999999999999E-2</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
@@ -671,7 +671,7 @@
         <v>2.4900000000000002</v>
       </c>
       <c r="C20" s="3">
-        <v>2.8299999999999999E-2</v>
+        <v>2.0799999999999999E-2</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
@@ -682,7 +682,7 @@
         <v>2.48</v>
       </c>
       <c r="C21" s="3">
-        <v>4.7300000000000002E-2</v>
+        <v>2.81E-2</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">
@@ -693,7 +693,7 @@
         <v>2.33</v>
       </c>
       <c r="C22" s="3">
-        <v>4.1799999999999997E-2</v>
+        <v>0.10730000000000001</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
@@ -704,7 +704,7 @@
         <v>2.2400000000000002</v>
       </c>
       <c r="C23" s="3">
-        <v>1.72E-2</v>
+        <v>-1E-3</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.3">
@@ -715,7 +715,7 @@
         <v>2.39</v>
       </c>
       <c r="C24" s="3">
-        <v>-2.3400000000000001E-2</v>
+        <v>-2.6200000000000001E-2</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.3">
@@ -726,7 +726,7 @@
         <v>2.44</v>
       </c>
       <c r="C25" s="3">
-        <v>4.1399999999999999E-2</v>
+        <v>3.4000000000000002E-2</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.3">
@@ -737,7 +737,7 @@
         <v>2.19</v>
       </c>
       <c r="C26" s="3">
-        <v>3.3099999999999997E-2</v>
+        <v>6.4500000000000002E-2</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.3">
@@ -748,7 +748,7 @@
         <v>2.39</v>
       </c>
       <c r="C27" s="3">
-        <v>2.12E-2</v>
+        <v>5.9999999999999995E-4</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.3">
@@ -759,7 +759,7 @@
         <v>2.7</v>
       </c>
       <c r="C28" s="3">
-        <v>-2.69E-2</v>
+        <v>-3.9300000000000002E-2</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.3">
@@ -770,7 +770,7 @@
         <v>2.75</v>
       </c>
       <c r="C29" s="3">
-        <v>3.5200000000000002E-2</v>
+        <v>1.1599999999999999E-2</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.3">
@@ -781,7 +781,7 @@
         <v>2.79</v>
       </c>
       <c r="C30" s="3">
-        <v>3.4099999999999998E-2</v>
+        <v>3.6400000000000002E-2</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.3">
@@ -792,7 +792,7 @@
         <v>2.5099999999999998</v>
       </c>
       <c r="C31" s="3">
-        <v>5.3900000000000003E-2</v>
+        <v>7.1900000000000006E-2</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.3">
@@ -803,7 +803,7 @@
         <v>2.96</v>
       </c>
       <c r="C32" s="3">
-        <v>4.7999999999999996E-3</v>
+        <v>-1.29E-2</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.3">
@@ -814,7 +814,7 @@
         <v>3.59</v>
       </c>
       <c r="C33" s="3">
-        <v>-6.8099999999999994E-2</v>
+        <v>-5.5899999999999998E-2</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.3">
@@ -825,7 +825,7 @@
         <v>3.21</v>
       </c>
       <c r="C34" s="3">
-        <v>8.7099999999999997E-2</v>
+        <v>7.46E-2</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.3">
@@ -836,7 +836,7 @@
         <v>3.86</v>
       </c>
       <c r="C35" s="3">
-        <v>-2.2200000000000001E-2</v>
+        <v>-6.0900000000000003E-2</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.3">
@@ -847,7 +847,7 @@
         <v>4.6900000000000004</v>
       </c>
       <c r="C36" s="3">
-        <v>-9.7000000000000003E-3</v>
+        <v>-2.2599999999999999E-2</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.3">
@@ -858,7 +858,7 @@
         <v>3.84</v>
       </c>
       <c r="C37" s="3">
-        <v>9.0700000000000003E-2</v>
+        <v>0.13780000000000001</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.3">
@@ -869,7 +869,7 @@
         <v>4.0599999999999996</v>
       </c>
       <c r="C38" s="3">
-        <v>4.82E-2</v>
+        <v>9.7000000000000003E-3</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.3">
@@ -880,7 +880,7 @@
         <v>3.86</v>
       </c>
       <c r="C39" s="3">
-        <v>7.9500000000000001E-2</v>
+        <v>6.8900000000000003E-2</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.3">
@@ -891,7 +891,7 @@
         <v>4.13</v>
       </c>
       <c r="C40" s="3">
-        <v>2.1899999999999999E-2</v>
+        <v>1.21E-2</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.3">
@@ -902,7 +902,7 @@
         <v>4.18</v>
       </c>
       <c r="C41" s="3">
-        <v>4.7699999999999999E-2</v>
+        <v>3.5099999999999999E-2</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.3">
@@ -913,7 +913,7 @@
         <v>4.62</v>
       </c>
       <c r="C42" s="3">
-        <v>-4.5999999999999999E-3</v>
+        <v>7.1000000000000004E-3</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.3">
@@ -924,7 +924,7 @@
         <v>4.84</v>
       </c>
       <c r="C43" s="3">
-        <v>2E-3</v>
+        <v>3.6499999999999998E-2</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.3">
@@ -935,7 +935,7 @@
         <v>5.7</v>
       </c>
       <c r="C44" s="3">
-        <v>-4.9500000000000002E-2</v>
+        <v>-9.1800000000000007E-2</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.3">
@@ -946,7 +946,7 @@
         <v>6.03</v>
       </c>
       <c r="C45" s="3">
-        <v>2.5700000000000001E-2</v>
+        <v>-2.5999999999999999E-3</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.3">
@@ -957,7 +957,7 @@
         <v>7.65</v>
       </c>
       <c r="C46" s="3">
-        <v>-8.09E-2</v>
+        <v>-5.0700000000000002E-2</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.3">
@@ -968,7 +968,7 @@
         <v>6.39</v>
       </c>
       <c r="C47" s="3">
-        <v>0.1837</v>
+        <v>0.1211</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.3">
@@ -979,7 +979,7 @@
         <v>5.93</v>
       </c>
       <c r="C48" s="3">
-        <v>0.1101</v>
+        <v>0.1323</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.3">
@@ -990,7 +990,7 @@
         <v>6.36</v>
       </c>
       <c r="C49" s="3">
-        <v>7.2599999999999998E-2</v>
+        <v>5.6899999999999999E-2</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.3">
@@ -1001,7 +1001,7 @@
         <v>6.74</v>
       </c>
       <c r="C50" s="3">
-        <v>1.14E-2</v>
+        <v>-1.11E-2</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.3">
@@ -1012,7 +1012,7 @@
         <v>7.43</v>
       </c>
       <c r="C51" s="3">
-        <v>3.0599999999999999E-2</v>
+        <v>4.3499999999999997E-2</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.3">
@@ -1023,7 +1023,7 @@
         <v>8</v>
       </c>
       <c r="C52" s="3">
-        <v>0.1464</v>
+        <v>9.1999999999999998E-2</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.3">
@@ -1034,7 +1034,7 @@
         <v>6.87</v>
       </c>
       <c r="C53" s="3">
-        <v>0.1865</v>
+        <v>0.16750000000000001</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.3">
@@ -1045,7 +1045,7 @@
         <v>7.69</v>
       </c>
       <c r="C54" s="3">
-        <v>1.7100000000000001E-2</v>
+        <v>-6.8999999999999999E-3</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.3">
@@ -1056,7 +1056,7 @@
         <v>9.01</v>
       </c>
       <c r="C55" s="3">
-        <v>-6.9999999999999999E-4</v>
+        <v>-1.18E-2</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.3">
@@ -1067,7 +1067,7 @@
         <v>10.39</v>
       </c>
       <c r="C56" s="3">
-        <v>-4.1799999999999997E-2</v>
+        <v>-1.23E-2</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.3">
@@ -1078,7 +1078,7 @@
         <v>12.84</v>
       </c>
       <c r="C57" s="3">
-        <v>-2.76E-2</v>
+        <v>-3.95E-2</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.3">
@@ -1089,7 +1089,7 @@
         <v>13.72</v>
       </c>
       <c r="C58" s="3">
-        <v>-1.24E-2</v>
+        <v>1.8599999999999998E-2</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.3">
@@ -1100,7 +1100,7 @@
         <v>10.54</v>
       </c>
       <c r="C59" s="3">
-        <v>0.42559999999999998</v>
+        <v>0.40360000000000001</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.3">
@@ -1111,7 +1111,7 @@
         <v>11.83</v>
       </c>
       <c r="C60" s="3">
-        <v>6.2600000000000003E-2</v>
+        <v>6.4999999999999997E-3</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.3">
@@ -1122,7 +1122,7 @@
         <v>11.5</v>
       </c>
       <c r="C61" s="3">
-        <v>0.1686</v>
+        <v>0.15479999999999999</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.3">
@@ -1133,7 +1133,7 @@
         <v>9.26</v>
       </c>
       <c r="C62" s="3">
-        <v>0.3009</v>
+        <v>0.30969999999999998</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.3">
@@ -1144,7 +1144,7 @@
         <v>7.11</v>
       </c>
       <c r="C63" s="3">
-        <v>0.19850000000000001</v>
+        <v>0.24529999999999999</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.3">
@@ -1155,7 +1155,7 @@
         <v>8.99</v>
       </c>
       <c r="C64" s="3">
-        <v>-2.7000000000000001E-3</v>
+        <v>-2.7099999999999999E-2</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.3">
@@ -1166,7 +1166,7 @@
         <v>9.11</v>
       </c>
       <c r="C65" s="3">
-        <v>0.107</v>
+        <v>9.6699999999999994E-2</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.3">
@@ -1177,7 +1177,7 @@
         <v>7.84</v>
       </c>
       <c r="C66" s="3">
-        <v>0.1623</v>
+        <v>0.18110000000000001</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.3">
@@ -1188,7 +1188,7 @@
         <v>8.08</v>
       </c>
       <c r="C67" s="3">
-        <v>6.7799999999999999E-2</v>
+        <v>6.1800000000000001E-2</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.3">
@@ -1199,7 +1199,7 @@
         <v>7.09</v>
       </c>
       <c r="C68" s="3">
-        <v>0.19889999999999999</v>
+        <v>0.193</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.3">
@@ -1210,7 +1210,7 @@
         <v>6.77</v>
       </c>
       <c r="C69" s="3">
-        <v>9.3899999999999997E-2</v>
+        <v>8.0500000000000002E-2</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.3">
@@ -1221,7 +1221,7 @@
         <v>5.77</v>
       </c>
       <c r="C70" s="3">
-        <v>0.13189999999999999</v>
+        <v>0.18240000000000001</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.3">
@@ -1232,7 +1232,7 @@
         <v>7.81</v>
       </c>
       <c r="C71" s="3">
-        <v>-5.7599999999999998E-2</v>
+        <v>-7.7700000000000005E-2</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.3">
@@ -1243,7 +1243,7 @@
         <v>5.71</v>
       </c>
       <c r="C72" s="3">
-        <v>0.27200000000000002</v>
+        <v>0.31669999999999998</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.3">
@@ -1254,7 +1254,7 @@
         <v>6.3</v>
       </c>
       <c r="C73" s="3">
-        <v>1.4E-2</v>
+        <v>-9.2999999999999992E-3</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.3">
@@ -1265,7 +1265,7 @@
         <v>5.81</v>
       </c>
       <c r="C74" s="3">
-        <v>0.1295</v>
+        <v>0.1585</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.3">
@@ -1276,7 +1276,7 @@
         <v>4.6500000000000004</v>
       </c>
       <c r="C75" s="3">
-        <v>0.1076</v>
+        <v>0.13059999999999999</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.3">
@@ -1287,7 +1287,7 @@
         <v>6.28</v>
       </c>
       <c r="C76" s="3">
-        <v>-7.4499999999999997E-2</v>
+        <v>-8.9599999999999999E-2</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.3">
@@ -1298,7 +1298,7 @@
         <v>5.24</v>
       </c>
       <c r="C77" s="3">
-        <v>0.12870000000000001</v>
+        <v>0.21479999999999999</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.3">
@@ -1309,7 +1309,7 @@
         <v>5.09</v>
       </c>
       <c r="C78" s="3">
-        <v>0.1065</v>
+        <v>3.6999999999999998E-2</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.3">
@@ -1320,7 +1320,7 @@
         <v>4.03</v>
       </c>
       <c r="C79" s="3">
-        <v>0.1633</v>
+        <v>0.1784</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.3">
@@ -1331,7 +1331,7 @@
         <v>4.2699999999999996</v>
       </c>
       <c r="C80" s="3">
-        <v>5.2699999999999997E-2</v>
+        <v>1.4500000000000001E-2</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.3">
@@ -1342,7 +1342,7 @@
         <v>4.2300000000000004</v>
       </c>
       <c r="C81" s="3">
-        <v>8.72E-2</v>
+        <v>8.5099999999999995E-2</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.3">
@@ -1353,7 +1353,7 @@
         <v>4.47</v>
       </c>
       <c r="C82" s="3">
-        <v>5.8700000000000002E-2</v>
+        <v>7.8100000000000003E-2</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.3">
@@ -1364,7 +1364,7 @@
         <v>4.5599999999999996</v>
       </c>
       <c r="C83" s="3">
-        <v>3.2399999999999998E-2</v>
+        <v>1.1900000000000001E-2</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.3">
@@ -1375,7 +1375,7 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="C84" s="3">
-        <v>2.5999999999999999E-2</v>
+        <v>9.8799999999999999E-2</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.3">
@@ -1386,7 +1386,7 @@
         <v>2.42</v>
       </c>
       <c r="C85" s="3">
-        <v>8.7800000000000003E-2</v>
+        <v>0.25869999999999999</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.3">
@@ -1397,7 +1397,7 @@
         <v>3.59</v>
       </c>
       <c r="C86" s="3">
-        <v>3.0200000000000001E-2</v>
+        <v>-0.14799999999999999</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.3">
@@ -1408,7 +1408,7 @@
         <v>3.29</v>
       </c>
       <c r="C87" s="3">
-        <v>0.1244</v>
+        <v>0.1014</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.3">
@@ -1419,7 +1419,7 @@
         <v>1.98</v>
       </c>
       <c r="C88" s="3">
-        <v>0.17949999999999999</v>
+        <v>0.27900000000000003</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.3">
@@ -1430,7 +1430,7 @@
         <v>1.72</v>
       </c>
       <c r="C89" s="3">
-        <v>0.10680000000000001</v>
+        <v>3.4299999999999997E-2</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.3">
@@ -1441,7 +1441,7 @@
         <v>2.9</v>
       </c>
       <c r="C90" s="3">
-        <v>-7.0699999999999999E-2</v>
+        <v>-0.1278</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.3">
@@ -1452,7 +1452,7 @@
         <v>2.21</v>
       </c>
       <c r="C91" s="3">
-        <v>0.17280000000000001</v>
+        <v>0.24709999999999999</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.3">
@@ -1463,7 +1463,7 @@
         <v>2.2400000000000002</v>
       </c>
       <c r="C92" s="3">
-        <v>-1.0200000000000001E-2</v>
+        <v>-6.4999999999999997E-3</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.3">

--- a/ibbotson.xlsx
+++ b/ibbotson.xlsx
@@ -5,15 +5,16 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ansa1\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ansa1\OneDrive\Desktop\treasury-bonds\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25A46C0B-5877-43A3-80B6-013808E59D55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6559B67-00D3-43D2-8F12-2B34308CA771}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="2" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="3" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -33,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="10">
   <si>
     <t>Long</t>
   </si>
@@ -42,6 +43,27 @@
   </si>
   <si>
     <t>Returns</t>
+  </si>
+  <si>
+    <t>Volatility</t>
+  </si>
+  <si>
+    <t>The usual annual volatility</t>
+  </si>
+  <si>
+    <t>Same as in the main data library</t>
+  </si>
+  <si>
+    <t>Long-term government rates</t>
+  </si>
+  <si>
+    <t>1926-2015</t>
+  </si>
+  <si>
+    <t>1928-2025</t>
+  </si>
+  <si>
+    <t>Ibbotson SBBI long-term government rates</t>
   </si>
 </sst>
 </file>
@@ -121,7 +143,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -145,6 +167,7 @@
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -449,15 +472,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:C102"/>
+  <dimension ref="A1:D102"/>
   <sheetFormatPr defaultRowHeight="20.25" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="17.140625" style="5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14" style="3" customWidth="1"/>
     <col min="3" max="3" width="13.7109375" style="3" customWidth="1"/>
+    <col min="4" max="4" width="14" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
         <v>1</v>
       </c>
@@ -467,8 +491,11 @@
       <c r="C1" s="7" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D1" s="7" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="6">
         <v>1925</v>
       </c>
@@ -476,7 +503,7 @@
         <v>3.8</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="6">
         <v>1926</v>
       </c>
@@ -487,7 +514,7 @@
         <v>7.7700000000000005E-2</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="6">
         <v>1927</v>
       </c>
@@ -498,7 +525,7 @@
         <v>8.9300000000000004E-2</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="6">
         <v>1928</v>
       </c>
@@ -508,8 +535,11 @@
       <c r="C5" s="3">
         <v>1E-3</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D5" s="3">
+        <v>9.3800000000000008</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="6">
         <v>1929</v>
       </c>
@@ -519,8 +549,11 @@
       <c r="C6" s="3">
         <v>3.4200000000000001E-2</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D6" s="3">
+        <v>23.76</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="6">
         <v>1930</v>
       </c>
@@ -530,8 +563,11 @@
       <c r="C7" s="3">
         <v>4.6600000000000003E-2</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D7" s="3">
+        <v>17.63</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="6">
         <v>1931</v>
       </c>
@@ -541,8 +577,11 @@
       <c r="C8" s="3">
         <v>-5.3100000000000001E-2</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D8" s="3">
+        <v>25.98</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="6">
         <v>1932</v>
       </c>
@@ -552,8 +591,11 @@
       <c r="C9" s="3">
         <v>0.16839999999999999</v>
       </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D9" s="3">
+        <v>33.590000000000003</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" s="6">
         <v>1933</v>
       </c>
@@ -563,8 +605,11 @@
       <c r="C10" s="3">
         <v>-6.9999999999999999E-4</v>
       </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D10" s="3">
+        <v>30.42</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" s="6">
         <v>1934</v>
       </c>
@@ -574,8 +619,11 @@
       <c r="C11" s="3">
         <v>0.1003</v>
       </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D11" s="3">
+        <v>16.600000000000001</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" s="6">
         <v>1935</v>
       </c>
@@ -585,8 +633,11 @@
       <c r="C12" s="3">
         <v>4.9799999999999997E-2</v>
       </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D12" s="3">
+        <v>17.93</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" s="6">
         <v>1936</v>
       </c>
@@ -596,8 +647,11 @@
       <c r="C13" s="3">
         <v>7.5200000000000003E-2</v>
       </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D13" s="3">
+        <v>12.22</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" s="6">
         <v>1937</v>
       </c>
@@ -607,8 +661,11 @@
       <c r="C14" s="3">
         <v>2.3E-3</v>
       </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D14" s="3">
+        <v>18.73</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" s="6">
         <v>1938</v>
       </c>
@@ -618,8 +675,11 @@
       <c r="C15" s="3">
         <v>5.5300000000000002E-2</v>
       </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D15" s="3">
+        <v>21.7</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" s="6">
         <v>1939</v>
       </c>
@@ -629,8 +689,11 @@
       <c r="C16" s="3">
         <v>5.9400000000000001E-2</v>
       </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D16" s="3">
+        <v>16.2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" s="6">
         <v>1940</v>
       </c>
@@ -640,8 +703,11 @@
       <c r="C17" s="3">
         <v>6.0900000000000003E-2</v>
       </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D17" s="3">
+        <v>13.97</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" s="6">
         <v>1941</v>
       </c>
@@ -651,8 +717,11 @@
       <c r="C18" s="3">
         <v>9.2999999999999992E-3</v>
       </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D18" s="3">
+        <v>9.4600000000000009</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" s="6">
         <v>1942</v>
       </c>
@@ -662,8 +731,11 @@
       <c r="C19" s="3">
         <v>3.2199999999999999E-2</v>
       </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D19" s="3">
+        <v>8.59</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" s="6">
         <v>1943</v>
       </c>
@@ -673,8 +745,11 @@
       <c r="C20" s="3">
         <v>2.0799999999999999E-2</v>
       </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D20" s="3">
+        <v>8.35</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" s="6">
         <v>1944</v>
       </c>
@@ -684,8 +759,11 @@
       <c r="C21" s="3">
         <v>2.81E-2</v>
       </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D21" s="3">
+        <v>5.75</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" s="6">
         <v>1945</v>
       </c>
@@ -695,8 +773,11 @@
       <c r="C22" s="3">
         <v>0.10730000000000001</v>
       </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D22" s="3">
+        <v>8.06</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" s="6">
         <v>1946</v>
       </c>
@@ -706,8 +787,11 @@
       <c r="C23" s="3">
         <v>-1E-3</v>
       </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D23" s="3">
+        <v>14.56</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" s="6">
         <v>1947</v>
       </c>
@@ -717,8 +801,11 @@
       <c r="C24" s="3">
         <v>-2.6200000000000001E-2</v>
       </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D24" s="3">
+        <v>8.99</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" s="6">
         <v>1948</v>
       </c>
@@ -728,8 +815,11 @@
       <c r="C25" s="3">
         <v>3.4000000000000002E-2</v>
       </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D25" s="3">
+        <v>9.69</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" s="6">
         <v>1949</v>
       </c>
@@ -739,8 +829,11 @@
       <c r="C26" s="3">
         <v>6.4500000000000002E-2</v>
       </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D26" s="3">
+        <v>7.36</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" s="6">
         <v>1950</v>
       </c>
@@ -750,8 +843,11 @@
       <c r="C27" s="3">
         <v>5.9999999999999995E-4</v>
       </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D27" s="3">
+        <v>9.4600000000000009</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" s="6">
         <v>1951</v>
       </c>
@@ -761,8 +857,11 @@
       <c r="C28" s="3">
         <v>-3.9300000000000002E-2</v>
       </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D28" s="3">
+        <v>6.79</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" s="6">
         <v>1952</v>
       </c>
@@ -772,8 +871,11 @@
       <c r="C29" s="3">
         <v>1.1599999999999999E-2</v>
       </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D29" s="3">
+        <v>4.9800000000000004</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" s="6">
         <v>1953</v>
       </c>
@@ -783,8 +885,11 @@
       <c r="C30" s="3">
         <v>3.6400000000000002E-2</v>
       </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D30" s="3">
+        <v>6.05</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31" s="6">
         <v>1954</v>
       </c>
@@ -794,8 +899,11 @@
       <c r="C31" s="3">
         <v>7.1900000000000006E-2</v>
       </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D31" s="3">
+        <v>5.92</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32" s="6">
         <v>1955</v>
       </c>
@@ -805,8 +913,11 @@
       <c r="C32" s="3">
         <v>-1.29E-2</v>
       </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D32" s="3">
+        <v>9.7200000000000006</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A33" s="6">
         <v>1956</v>
       </c>
@@ -816,8 +927,11 @@
       <c r="C33" s="3">
         <v>-5.5899999999999998E-2</v>
       </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D33" s="3">
+        <v>7.82</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A34" s="6">
         <v>1957</v>
       </c>
@@ -827,8 +941,11 @@
       <c r="C34" s="3">
         <v>7.46E-2</v>
       </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D34" s="3">
+        <v>8.18</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A35" s="6">
         <v>1958</v>
       </c>
@@ -838,8 +955,11 @@
       <c r="C35" s="3">
         <v>-6.0900000000000003E-2</v>
       </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D35" s="3">
+        <v>5.66</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A36" s="6">
         <v>1959</v>
       </c>
@@ -849,8 +969,11 @@
       <c r="C36" s="3">
         <v>-2.2599999999999999E-2</v>
       </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D36" s="3">
+        <v>5.92</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A37" s="6">
         <v>1960</v>
       </c>
@@ -860,8 +983,11 @@
       <c r="C37" s="3">
         <v>0.13780000000000001</v>
       </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D37" s="3">
+        <v>6.54</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A38" s="6">
         <v>1961</v>
       </c>
@@ -871,8 +997,11 @@
       <c r="C38" s="3">
         <v>9.7000000000000003E-3</v>
       </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D38" s="3">
+        <v>6.38</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A39" s="6">
         <v>1962</v>
       </c>
@@ -882,8 +1011,11 @@
       <c r="C39" s="3">
         <v>6.8900000000000003E-2</v>
       </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D39" s="3">
+        <v>10.46</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A40" s="6">
         <v>1963</v>
       </c>
@@ -893,8 +1025,11 @@
       <c r="C40" s="3">
         <v>1.21E-2</v>
       </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D40" s="3">
+        <v>5.42</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A41" s="6">
         <v>1964</v>
       </c>
@@ -904,8 +1039,11 @@
       <c r="C41" s="3">
         <v>3.5099999999999999E-2</v>
       </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D41" s="3">
+        <v>3.32</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A42" s="6">
         <v>1965</v>
       </c>
@@ -915,8 +1053,11 @@
       <c r="C42" s="3">
         <v>7.1000000000000004E-3</v>
       </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D42" s="3">
+        <v>4.37</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A43" s="6">
         <v>1966</v>
       </c>
@@ -926,8 +1067,11 @@
       <c r="C43" s="3">
         <v>3.6499999999999998E-2</v>
       </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D43" s="3">
+        <v>7.43</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A44" s="6">
         <v>1967</v>
       </c>
@@ -937,8 +1081,11 @@
       <c r="C44" s="3">
         <v>-9.1800000000000007E-2</v>
       </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D44" s="3">
+        <v>5.29</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A45" s="6">
         <v>1968</v>
       </c>
@@ -948,8 +1095,11 @@
       <c r="C45" s="3">
         <v>-2.5999999999999999E-3</v>
       </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D45" s="3">
+        <v>5.9</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A46" s="6">
         <v>1969</v>
       </c>
@@ -959,8 +1109,11 @@
       <c r="C46" s="3">
         <v>-5.0700000000000002E-2</v>
       </c>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D46" s="3">
+        <v>6.33</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A47" s="6">
         <v>1970</v>
       </c>
@@ -970,8 +1123,11 @@
       <c r="C47" s="3">
         <v>0.1211</v>
       </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D47" s="3">
+        <v>9.52</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A48" s="6">
         <v>1971</v>
       </c>
@@ -981,8 +1137,11 @@
       <c r="C48" s="3">
         <v>0.1323</v>
       </c>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D48" s="3">
+        <v>6.42</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A49" s="6">
         <v>1972</v>
       </c>
@@ -992,8 +1151,11 @@
       <c r="C49" s="3">
         <v>5.6899999999999999E-2</v>
       </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D49" s="3">
+        <v>5.01</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A50" s="6">
         <v>1973</v>
       </c>
@@ -1003,8 +1165,11 @@
       <c r="C50" s="3">
         <v>-1.11E-2</v>
       </c>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D50" s="3">
+        <v>9.9700000000000006</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A51" s="6">
         <v>1974</v>
       </c>
@@ -1014,8 +1179,11 @@
       <c r="C51" s="3">
         <v>4.3499999999999997E-2</v>
       </c>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D51" s="3">
+        <v>13.72</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A52" s="6">
         <v>1975</v>
       </c>
@@ -1025,8 +1193,11 @@
       <c r="C52" s="3">
         <v>9.1999999999999998E-2</v>
       </c>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D52" s="3">
+        <v>9.6999999999999993</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A53" s="6">
         <v>1976</v>
       </c>
@@ -1036,8 +1207,11 @@
       <c r="C53" s="3">
         <v>0.16750000000000001</v>
       </c>
-    </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D53" s="3">
+        <v>6.99</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A54" s="6">
         <v>1977</v>
       </c>
@@ -1047,8 +1221,11 @@
       <c r="C54" s="3">
         <v>-6.8999999999999999E-3</v>
       </c>
-    </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D54" s="3">
+        <v>5.72</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A55" s="6">
         <v>1978</v>
       </c>
@@ -1058,8 +1235,11 @@
       <c r="C55" s="3">
         <v>-1.18E-2</v>
       </c>
-    </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D55" s="3">
+        <v>7.92</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A56" s="6">
         <v>1979</v>
       </c>
@@ -1069,8 +1249,11 @@
       <c r="C56" s="3">
         <v>-1.23E-2</v>
       </c>
-    </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D56" s="3">
+        <v>6.84</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A57" s="6">
         <v>1980</v>
       </c>
@@ -1080,8 +1263,11 @@
       <c r="C57" s="3">
         <v>-3.95E-2</v>
       </c>
-    </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D57" s="3">
+        <v>10.37</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A58" s="6">
         <v>1981</v>
       </c>
@@ -1091,8 +1277,11 @@
       <c r="C58" s="3">
         <v>1.8599999999999998E-2</v>
       </c>
-    </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D58" s="3">
+        <v>8.48</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A59" s="6">
         <v>1982</v>
       </c>
@@ -1102,8 +1291,11 @@
       <c r="C59" s="3">
         <v>0.40360000000000001</v>
       </c>
-    </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D59" s="3">
+        <v>11.45</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A60" s="6">
         <v>1983</v>
       </c>
@@ -1113,8 +1305,11 @@
       <c r="C60" s="3">
         <v>6.4999999999999997E-3</v>
       </c>
-    </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D60" s="3">
+        <v>8.39</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A61" s="6">
         <v>1984</v>
       </c>
@@ -1124,8 +1319,11 @@
       <c r="C61" s="3">
         <v>0.15479999999999999</v>
       </c>
-    </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D61" s="3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A62" s="6">
         <v>1985</v>
       </c>
@@ -1135,8 +1333,11 @@
       <c r="C62" s="3">
         <v>0.30969999999999998</v>
       </c>
-    </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D62" s="3">
+        <v>6.39</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A63" s="6">
         <v>1986</v>
       </c>
@@ -1146,8 +1347,11 @@
       <c r="C63" s="3">
         <v>0.24529999999999999</v>
       </c>
-    </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D63" s="3">
+        <v>9.2899999999999991</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A64" s="6">
         <v>1987</v>
       </c>
@@ -1157,8 +1361,11 @@
       <c r="C64" s="3">
         <v>-2.7099999999999999E-2</v>
       </c>
-    </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D64" s="3">
+        <v>21.25</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A65" s="6">
         <v>1988</v>
       </c>
@@ -1168,8 +1375,11 @@
       <c r="C65" s="3">
         <v>9.6699999999999994E-2</v>
       </c>
-    </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D65" s="3">
+        <v>10.82</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A66" s="6">
         <v>1989</v>
       </c>
@@ -1179,8 +1389,11 @@
       <c r="C66" s="3">
         <v>0.18110000000000001</v>
       </c>
-    </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D66" s="3">
+        <v>8.2799999999999994</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A67" s="6">
         <v>1990</v>
       </c>
@@ -1190,8 +1403,11 @@
       <c r="C67" s="3">
         <v>6.1800000000000001E-2</v>
       </c>
-    </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D67" s="3">
+        <v>10.06</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A68" s="6">
         <v>1991</v>
       </c>
@@ -1201,8 +1417,11 @@
       <c r="C68" s="3">
         <v>0.193</v>
       </c>
-    </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D68" s="3">
+        <v>8.99</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A69" s="6">
         <v>1992</v>
       </c>
@@ -1212,8 +1431,11 @@
       <c r="C69" s="3">
         <v>8.0500000000000002E-2</v>
       </c>
-    </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D69" s="3">
+        <v>6.1</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A70" s="6">
         <v>1993</v>
       </c>
@@ -1223,8 +1445,11 @@
       <c r="C70" s="3">
         <v>0.18240000000000001</v>
       </c>
-    </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D70" s="3">
+        <v>5.42</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A71" s="6">
         <v>1994</v>
       </c>
@@ -1234,8 +1459,11 @@
       <c r="C71" s="3">
         <v>-7.7700000000000005E-2</v>
       </c>
-    </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D71" s="3">
+        <v>6.21</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A72" s="6">
         <v>1995</v>
       </c>
@@ -1245,8 +1473,11 @@
       <c r="C72" s="3">
         <v>0.31669999999999998</v>
       </c>
-    </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D72" s="3">
+        <v>4.91</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A73" s="6">
         <v>1996</v>
       </c>
@@ -1256,8 +1487,11 @@
       <c r="C73" s="3">
         <v>-9.2999999999999992E-3</v>
       </c>
-    </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D73" s="3">
+        <v>7.43</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A74" s="6">
         <v>1997</v>
       </c>
@@ -1267,8 +1501,11 @@
       <c r="C74" s="3">
         <v>0.1585</v>
       </c>
-    </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D74" s="3">
+        <v>11.45</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A75" s="6">
         <v>1998</v>
       </c>
@@ -1278,8 +1515,11 @@
       <c r="C75" s="3">
         <v>0.13059999999999999</v>
       </c>
-    </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D75" s="3">
+        <v>12.81</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A76" s="6">
         <v>1999</v>
       </c>
@@ -1289,8 +1529,11 @@
       <c r="C76" s="3">
         <v>-8.9599999999999999E-2</v>
       </c>
-    </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D76" s="3">
+        <v>11.37</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A77" s="6">
         <v>2000</v>
       </c>
@@ -1300,8 +1543,11 @@
       <c r="C77" s="3">
         <v>0.21479999999999999</v>
       </c>
-    </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D77" s="3">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A78" s="6">
         <v>2001</v>
       </c>
@@ -1311,8 +1557,11 @@
       <c r="C78" s="3">
         <v>3.6999999999999998E-2</v>
       </c>
-    </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D78" s="3">
+        <v>13.58</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A79" s="6">
         <v>2002</v>
       </c>
@@ -1322,8 +1571,11 @@
       <c r="C79" s="3">
         <v>0.1784</v>
       </c>
-    </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D79" s="3">
+        <v>16.350000000000001</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A80" s="6">
         <v>2003</v>
       </c>
@@ -1333,8 +1585,11 @@
       <c r="C80" s="3">
         <v>1.4500000000000001E-2</v>
       </c>
-    </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D80" s="3">
+        <v>10.74</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A81" s="6">
         <v>2004</v>
       </c>
@@ -1344,8 +1599,11 @@
       <c r="C81" s="3">
         <v>8.5099999999999995E-2</v>
       </c>
-    </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D81" s="3">
+        <v>6.99</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A82" s="6">
         <v>2005</v>
       </c>
@@ -1355,8 +1613,11 @@
       <c r="C82" s="3">
         <v>7.8100000000000003E-2</v>
       </c>
-    </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D82" s="3">
+        <v>6.48</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A83" s="6">
         <v>2006</v>
       </c>
@@ -1366,8 +1627,11 @@
       <c r="C83" s="3">
         <v>1.1900000000000001E-2</v>
       </c>
-    </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D83" s="3">
+        <v>6.31</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A84" s="6">
         <v>2007</v>
       </c>
@@ -1377,8 +1641,11 @@
       <c r="C84" s="3">
         <v>9.8799999999999999E-2</v>
       </c>
-    </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D84" s="3">
+        <v>10.09</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A85" s="6">
         <v>2008</v>
       </c>
@@ -1388,8 +1655,11 @@
       <c r="C85" s="3">
         <v>0.25869999999999999</v>
       </c>
-    </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D85" s="3">
+        <v>25.84</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A86" s="6">
         <v>2009</v>
       </c>
@@ -1399,8 +1669,11 @@
       <c r="C86" s="3">
         <v>-0.14799999999999999</v>
       </c>
-    </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D86" s="3">
+        <v>17.18</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A87" s="6">
         <v>2010</v>
       </c>
@@ -1410,8 +1683,11 @@
       <c r="C87" s="3">
         <v>0.1014</v>
       </c>
-    </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D87" s="3">
+        <v>11.38</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A88" s="6">
         <v>2011</v>
       </c>
@@ -1421,8 +1697,11 @@
       <c r="C88" s="3">
         <v>0.27900000000000003</v>
       </c>
-    </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D88" s="3">
+        <v>14.71</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A89" s="6">
         <v>2012</v>
       </c>
@@ -1432,8 +1711,11 @@
       <c r="C89" s="3">
         <v>3.4299999999999997E-2</v>
       </c>
-    </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D89" s="3">
+        <v>8.0399999999999991</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A90" s="6">
         <v>2013</v>
       </c>
@@ -1443,8 +1725,11 @@
       <c r="C90" s="3">
         <v>-0.1278</v>
       </c>
-    </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D90" s="3">
+        <v>6.97</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A91" s="6">
         <v>2014</v>
       </c>
@@ -1454,8 +1739,11 @@
       <c r="C91" s="3">
         <v>0.24709999999999999</v>
       </c>
-    </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D91" s="3">
+        <v>7.17</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A92" s="6">
         <v>2015</v>
       </c>
@@ -1465,119 +1753,182 @@
       <c r="C92" s="3">
         <v>-6.4999999999999997E-3</v>
       </c>
-    </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D92" s="3">
+        <v>9.77</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A93" s="6">
         <v>2016</v>
       </c>
       <c r="B93" s="2">
         <v>2.4900000000000002</v>
       </c>
-      <c r="C93" s="8">
-        <v>1.8326597016962376E-2</v>
-      </c>
-    </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C93" s="8"/>
+      <c r="D93" s="3">
+        <v>8.26</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A94" s="6">
         <v>2017</v>
       </c>
       <c r="B94" s="2">
         <v>2.4</v>
       </c>
-      <c r="C94" s="8">
-        <v>3.1282123925046035E-2</v>
-      </c>
-    </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C94" s="8"/>
+      <c r="D94" s="3">
+        <v>4.21</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A95" s="6">
         <v>2018</v>
       </c>
       <c r="B95" s="2">
         <v>2.83</v>
       </c>
-      <c r="C95" s="8">
-        <v>8.4038021812349317E-3</v>
-      </c>
-    </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C95" s="8"/>
+      <c r="D95" s="3">
+        <v>10.77</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A96" s="6">
         <v>2019</v>
       </c>
       <c r="B96" s="2">
         <v>1.86</v>
       </c>
-      <c r="C96" s="8">
-        <v>8.708692144400354E-2</v>
-      </c>
-    </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C96" s="8"/>
+      <c r="D96" s="3">
+        <v>7.87</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A97" s="6">
         <v>2020</v>
       </c>
       <c r="B97" s="2">
         <v>0.93</v>
       </c>
-      <c r="C97" s="8">
-        <v>0.10811901242710809</v>
-      </c>
-    </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C97" s="8"/>
+      <c r="D97" s="3">
+        <v>21.85</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A98" s="6">
         <v>2021</v>
       </c>
       <c r="B98" s="2">
         <v>1.47</v>
       </c>
-      <c r="C98" s="8">
-        <v>-3.7261235372969881E-2</v>
-      </c>
-    </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C98" s="8"/>
+      <c r="D98" s="3">
+        <v>8.26</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A99" s="6">
         <v>2022</v>
       </c>
       <c r="B99" s="2">
         <v>3.62</v>
       </c>
-      <c r="C99" s="8">
-        <v>-0.13769242682515725</v>
-      </c>
-    </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C99" s="8"/>
+      <c r="D99" s="3">
+        <v>15.24</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A100" s="6">
         <v>2023</v>
       </c>
       <c r="B100" s="2">
         <v>4.0199999999999996</v>
       </c>
-      <c r="C100" s="8">
-        <v>4.2422339622889993E-2</v>
-      </c>
-    </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C100" s="8"/>
+      <c r="D100" s="3">
+        <v>8.24</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A101" s="6">
         <v>2024</v>
       </c>
       <c r="B101" s="2">
         <v>4.3899999999999997</v>
       </c>
-      <c r="C101" s="8">
-        <v>-2.924774839147104E-3</v>
-      </c>
-    </row>
-    <row r="102" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C101" s="8"/>
+      <c r="D101" s="3">
+        <v>7.98</v>
+      </c>
+    </row>
+    <row r="102" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A102" s="6">
         <v>2025</v>
       </c>
       <c r="B102" s="2">
         <v>4.1399999999999997</v>
       </c>
-      <c r="C102" s="8">
-        <v>8.4903480921744379E-2</v>
+      <c r="C102" s="8"/>
+      <c r="D102" s="3">
+        <v>11.77</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3E602789-7EA1-45AB-9C68-AAE5017FD5F5}">
+  <dimension ref="A1:C4"/>
+  <sheetFormatPr defaultRowHeight="20.25" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" style="9" customWidth="1"/>
+    <col min="2" max="2" width="23" style="9" customWidth="1"/>
+    <col min="3" max="16384" width="9.140625" style="9"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="9" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B3" s="9" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>9</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/ibbotson.xlsx
+++ b/ibbotson.xlsx
@@ -8,13 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ansa1\OneDrive\Desktop\treasury-bonds\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6559B67-00D3-43D2-8F12-2B34308CA771}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57DE262C-A289-463F-AD93-8E9363828D43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="2" r:id="rId1"/>
-    <sheet name="Sheet1" sheetId="3" r:id="rId2"/>
+    <sheet name="readme" sheetId="3" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
